--- a/02_加值成品/生物/生物7-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物7-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物7-2 生物的分類　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國一(七年級) 生物7-2 生物的分類　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>分類階層由大到小是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>界門綱目科屬種</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>統一名稱避免混淆</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>越低的相同階層</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>兩個(屬名+種小名)</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>階層</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>分類的基本單位是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>種</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>研究與溝通</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>二名法</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>斜體屬名大寫</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>最小</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>學名採什麼命名法？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>種</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>二名法</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>研究與溝通</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>交配產生後代</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>屬+種</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>學名用什麼文字？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>種</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>拉丁文</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>越接近</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>特徵</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>統一</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>最大的分類階層是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>交配產生後代</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>林奈</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>界</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>拉丁文</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>最大</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>學名由屬名加什麼組成？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>拉丁文</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>種小名</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>種</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>研究與溝通</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>二名</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>分類依據生物的？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>特徵</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>研究與溝通</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>親緣關係</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>二名法</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>構造</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>分類幫助了解生物的？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>界</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>研究與溝通</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>親緣關係</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>二名法</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>親緣</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>界門綱目科屬種中最小的是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>二名法</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>種</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>越接近</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>界</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>最小</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>同一物種的個體能？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>種</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>親緣關係</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>交配產生後代</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>二名法</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>種</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物7-2 生物的分類　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國一(七年級) 生物7-2 生物的分類　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>種與界哪個範圍大？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>林奈</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>二名法</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>界</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>種小名</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>較大</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>學名書寫格式？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>種小名</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>拉丁文</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>斜體屬名大寫</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>特徵</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>格式</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>分類反映生物間的？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>親緣關係</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>研究與溝通</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>種小名</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>界</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>演化</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>動物界植物界屬哪個階層？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>拉丁文</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>界</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>種</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>越接近</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>最大</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>越低階層生物親緣關係？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>越接近</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>拉丁文</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>界</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>種小名</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>越近</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>二名法由誰推廣？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>林奈</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>斜體屬名大寫</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>特徵</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>界</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>命名</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>同種生物可否交配繁殖後代？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>可(能繁衍後代)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>界門綱目科屬種越低親緣越近方便研究</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>統一名稱避免混淆</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>精確唯一國際通用</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>種定義</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>分類系統的用途？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>研究與溝通</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>越接近</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>二名法</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>親緣關係</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>工具</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>學名由幾個部分組成？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>系統歸類便於記錄比較與保育</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>避免各地俗名混淆全球通用</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>可(能繁衍後代)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>兩個(屬名+種小名)</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>二名</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>親緣關係越近的生物分在？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>越低的相同階層</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>精確唯一國際通用</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>界門綱目科屬種越低親緣越近方便研究</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>避免各地俗名混淆全球通用</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>親緣</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物7-2 生物的分類　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國一(七年級) 生物7-2 生物的分類　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>說明分類階層由大到小及意義？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>界門綱目科屬種</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>界門綱目科屬種越低親緣越近方便研究</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>系統歸類便於記錄比較與保育</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>越低的相同階層</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>階層</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何學名採統一的二名法？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>親緣近的分在較低相同階層</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>外表相似親緣未必接近</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>避免各地俗名混淆全球通用</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>可(能繁衍後代)</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>統一</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>分類如何反映生物的演化親緣？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>細胞構造營養方式等基本特徵</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>統一名稱避免混淆</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>親緣近的分在較低相同階層</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>外表相似親緣未必接近</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>親緣</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>種作為基本單位的意義？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>同種可交配繁衍後代為分類基礎</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>界門綱目科屬種</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>系統歸類便於記錄比較與保育</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>可(能繁衍後代)</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>基本</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>分類依據為何不能只看外表？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>統一名稱避免混淆</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>避免各地俗名混淆全球通用</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>親緣近的分在較低相同階層</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>外表相似未必親緣近需看構造</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>依據</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>生物分界的依據大致為何？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>界門綱目科屬種越低親緣越近方便研究</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>外表相似未必親緣近需看構造</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>兩個(屬名+種小名)</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>細胞構造營養方式等基本特徵</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>分界</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>學名比俗名的優點？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>同種可交配繁衍後代為分類基礎</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>精確唯一國際通用</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>界門綱目科屬種</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>兩個(屬名+種小名)</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>優點</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>分類系統如何幫助生物多樣性研究？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>系統歸類便於記錄比較與保育</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>外表相似未必親緣近需看構造</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>親緣近的分在較低相同階層</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>避免各地俗名混淆全球通用</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何不能只用外表相似來分類？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>外表相似親緣未必接近</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>越低的相同階層</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>外表相似未必親緣近需看構造</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>精確唯一國際通用</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>外表</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>二名法對全球科學交流的意義？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>外表相似未必親緣近需看構造</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>統一名稱避免混淆</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>越低的相同階層</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>兩個(屬名+種小名)</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>統一</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/生物/生物7-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物7-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>階層</t>
+          <t>階層順序：生物分類由大範圍到小範圍依序是界、門、綱、目、科、屬、種</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>最小</t>
+          <t>最小單位：種是分類階層中最小、最基本的單位，範圍最小最精確</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>屬+種</t>
+          <t>二名法：學名由屬名加種小名兩部分組成，所以叫做二名法</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>統一拉丁文：為了讓全世界的人都看得懂，學名一律使用拉丁文書寫</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>最大</t>
+          <t>最大階層：界是分類系統中範圍最大的一層，包含最多種類的生物</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>二名</t>
+          <t>屬名加種小名：學名的組成方式是先寫屬名，再加上種小名合成一個完整名稱</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>構造</t>
+          <t>依特徵分類：科學家依照生物的構造、特徵等相似程度來進行分類</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>親緣</t>
+          <t>了解親緣：透過分類系統，我們可以看出不同生物彼此關係的遠近</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>最小</t>
+          <t>最小：生物分類階層由大到小依序是界、門、綱、目、科、屬、種，種是最小、最基本的分類單位</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>種</t>
+          <t>種：同一物種的個體之間能夠互相交配，並產生具有生殖能力的後代，這是判斷是否為同一物種的重要依據</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>較大</t>
+          <t>界範圍較大：界是最大的分類階層，種是最小的，所以界包含的範圍遠大於種</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>格式</t>
+          <t>書寫格式：學名要用斜體字，且屬名的第一個字母要大寫，種小名則全部小寫</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>演化</t>
+          <t>反映親緣：分類階層愈接近的生物，彼此的親緣關係通常也愈接近</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>最大</t>
+          <t>屬於界：動物界、植物界都是分類系統中最頂層、範圍最大的界這個階層</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>越近</t>
+          <t>愈低愈接近：分類階層愈往下（愈接近種），生物之間的親緣關係就愈相近</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>命名</t>
+          <t>林奈推廣：瑞典科學家林奈建立並推廣了用二名法為生物命名的系統</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>種定義</t>
+          <t>可以繁衍：同一種的生物彼此交配可以產生後代，這是判斷是否同種的重要依據</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>工具</t>
+          <t>研究溝通：有了統一的分類系統，各國科學家在研究和交流時才不會混淆</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>二名</t>
+          <t>二名：生物學名採用二名法命名，由屬名加種小名兩部分組成，用來統一表示一個物種</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>親緣</t>
+          <t>親緣：分類階層越低（越接近種），代表生物之間的親緣關係越接近，例如同科的生物比同界的生物親緣關係更近</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>階層</t>
+          <t>階層意義：由界到種範圍逐漸縮小，階層愈低生物親緣愈接近，方便科學家精確研究與溝通</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>避免混淆：各地俗名常不一樣容易搞混，統一用拉丁文二名法可以讓全世界都通用無誤</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>親緣</t>
+          <t>反映演化：親緣關係接近、演化來源相近的生物，會被歸在較低、相同的分類階層中</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>基本</t>
+          <t>基本意義：能互相交配並產生可繁殖後代，是判斷生物屬於同一種的重要分類基礎</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>依據</t>
+          <t>不只看外表：外表相似的生物親緣不一定近，還要比對內部構造等特徵才準確</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>分界</t>
+          <t>分界依據：科學家依細胞構造、獲取營養的方式等最基本的特徵，把生物分成不同的界</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>優點</t>
+          <t>學名優點：學名對每種生物都是獨一無二又精確，而且全世界通用不會搞混</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>幫助研究：有系統地歸類生物，方便記錄、比較不同物種，也有利於推動保育工作</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>外表</t>
+          <t>外表：有些生物外表看起來相似，但實際上親緣關係可能相差很遠（例如趨同演化），所以分類不能只靠外表，還要參考構造、遺傳等更多證據</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>統一：不同國家、語言對同一種生物可能有不同俗名，容易造成混淆，二名法提供全世界通用、統一的學名，方便科學家溝通交流</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/生物/生物7-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物7-2_三種難度測驗卷.xlsx
@@ -568,17 +568,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>統一名稱避免混淆</t>
+          <t>精確唯一國際通用</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>越低的相同階層</t>
+          <t>親緣近的分在較低相同階層</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>兩個(屬名+種小名)</t>
+          <t>可(能繁衍後代)</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>研究與溝通</t>
+          <t>斜體屬名大寫</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
+          <t>特徵</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
           <t>二名法</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>斜體屬名大寫</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -763,22 +763,22 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
+          <t>林奈</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>種小名</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
           <t>拉丁文</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>種小名</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>種</t>
-        </is>
-      </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>研究與溝通</t>
+          <t>特徵</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>二名法</t>
+          <t>拉丁文</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>越接近</t>
+          <t>特徵</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>界</t>
+          <t>林奈</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>界門綱目科屬種</t>
+          <t>同種可交配繁衍後代為分類基礎</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>系統歸類便於記錄比較與保育</t>
+          <t>兩個(屬名+種小名)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>越低的相同階層</t>
+          <t>精確唯一國際通用</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
